--- a/business_forms/019_ai_impact_on_small_businesses--business_forms.xlsx
+++ b/business_forms/019_ai_impact_on_small_businesses--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -923,8 +923,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -952,12 +952,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'retail_/_e-commerce',_'value':_'retail'}</t>
+          <t>retail_/_e-commerce</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Retail / E-commerce', 'value': 'retail'}</t>
+          <t>Retail / E-commerce</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'professional_services_(legal,_accounting,_etc.)',_'value':_'professional_services'}</t>
+          <t>professional_services_(legal,_accounting,_etc.)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Professional Services (Legal, Accounting, etc.)', 'value': 'professional_services'}</t>
+          <t>Professional Services (Legal, Accounting, etc.)</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'healthcare_&amp;_wellness',_'value':_'healthcare'}</t>
+          <t>healthcare_&amp;_wellness</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Healthcare &amp; Wellness', 'value': 'healthcare'}</t>
+          <t>Healthcare &amp; Wellness</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'hospitality_&amp;_food_service',_'value':_'hospitality'}</t>
+          <t>hospitality_&amp;_food_service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Hospitality &amp; Food Service', 'value': 'hospitality'}</t>
+          <t>Hospitality &amp; Food Service</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'manufacturing_&amp;_construction',_'value':_'manufacturing'}</t>
+          <t>manufacturing_&amp;_construction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Manufacturing &amp; Construction', 'value': 'manufacturing'}</t>
+          <t>Manufacturing &amp; Construction</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'technology_&amp;_software',_'value':_'technology'}</t>
+          <t>technology_&amp;_software</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Technology &amp; Software', 'value': 'technology'}</t>
+          <t>Technology &amp; Software</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'solopreneur_(1)',_'value':_1}</t>
+          <t>solopreneur_(1)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Solopreneur (1)', 'value': 1}</t>
+          <t>Solopreneur (1)</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'micro_(2-5)',_'value':_'2-5'}</t>
+          <t>micro_(2-5)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Micro (2-5)', 'value': '2-5'}</t>
+          <t>Micro (2-5)</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'small_(6-20)',_'value':_'6-20'}</t>
+          <t>small_(6-20)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Small (6-20)', 'value': '6-20'}</t>
+          <t>Small (6-20)</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'medium-small_(21-50)',_'value':_'21-50'}</t>
+          <t>medium-small_(21-50)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Medium-Small (21-50)', 'value': '21-50'}</t>
+          <t>Medium-Small (21-50)</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'medium_(51-100)',_'value':_'51-100'}</t>
+          <t>medium_(51-100)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Medium (51-100)', 'value': '51-100'}</t>
+          <t>Medium (51-100)</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_currently_using_or_considering',_'value':_'none'}</t>
+          <t>not_currently_using_or_considering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not currently using or considering', 'value': 'none'}</t>
+          <t>Not currently using or considering</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'actively_researching_/_planning',_'value':_'planning'}</t>
+          <t>actively_researching_/_planning</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Actively researching / Planning', 'value': 'planning'}</t>
+          <t>Actively researching / Planning</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'testing_/_pilot_programs_in_place',_'value':_'pilot'}</t>
+          <t>testing_/_pilot_programs_in_place</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Testing / Pilot programs in place', 'value': 'pilot'}</t>
+          <t>Testing / Pilot programs in place</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'fully_integrated_into_some_workflows',_'value':_'integrated'}</t>
+          <t>fully_integrated_into_some_workflows</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Fully integrated into some workflows', 'value': 'integrated'}</t>
+          <t>Fully integrated into some workflows</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'ai-first_business_model',_'value':_'ai_first'}</t>
+          <t>ai-first_business_model</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'AI-first business model', 'value': 'ai_first'}</t>
+          <t>AI-first business model</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'generative_ai_(chatgpt,_claude,_jasper)',_'value':_'gen_ai'}</t>
+          <t>generative_ai_(chatgpt,_claude,_jasper)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Generative AI (ChatGPT, Claude, Jasper)', 'value': 'gen_ai'}</t>
+          <t>Generative AI (ChatGPT, Claude, Jasper)</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'ai_chatbots_for_customer_service',_'value':_'chatbots'}</t>
+          <t>ai_chatbots_for_customer_service</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'AI Chatbots for Customer Service', 'value': 'chatbots'}</t>
+          <t>AI Chatbots for Customer Service</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'marketing_automation_with_ai',_'value':_'marketing_ai'}</t>
+          <t>marketing_automation_with_ai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing Automation with AI', 'value': 'marketing_ai'}</t>
+          <t>Marketing Automation with AI</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'ai-powered_analytics_/_forecasting',_'value':_'analytics'}</t>
+          <t>ai-powered_analytics_/_forecasting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'AI-powered Analytics / Forecasting', 'value': 'analytics'}</t>
+          <t>AI-powered Analytics / Forecasting</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'image_/_video_generation',_'value':_'creative_ai'}</t>
+          <t>image_/_video_generation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Image / Video Generation', 'value': 'creative_ai'}</t>
+          <t>Image / Video Generation</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'increased_efficiency_/_productivity',_'value':_'efficiency'}</t>
+          <t>increased_efficiency_/_productivity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Increased Efficiency / Productivity', 'value': 'efficiency'}</t>
+          <t>Increased Efficiency / Productivity</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'cost_savings_/_reduced_overheads',_'value':_'cost_savings'}</t>
+          <t>cost_savings_/_reduced_overheads</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Cost Savings / Reduced Overheads', 'value': 'cost_savings'}</t>
+          <t>Cost Savings / Reduced Overheads</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'improved_customer_experience',_'value':_'customer_exp'}</t>
+          <t>improved_customer_experience</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Improved Customer Experience', 'value': 'customer_exp'}</t>
+          <t>Improved Customer Experience</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'better_decision_making_/_insights',_'value':_'insights'}</t>
+          <t>better_decision_making_/_insights</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Better Decision Making / Insights', 'value': 'insights'}</t>
+          <t>Better Decision Making / Insights</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'creative_content_generation',_'value':_'content'}</t>
+          <t>creative_content_generation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Creative Content Generation', 'value': 'content'}</t>
+          <t>Creative Content Generation</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'high_implementation_costs',_'value':_'cost'}</t>
+          <t>high_implementation_costs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'High Implementation Costs', 'value': 'cost'}</t>
+          <t>High Implementation Costs</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_in-house_technical_expertise',_'value':_'lack_expertise'}</t>
+          <t>lack_of_in-house_technical_expertise</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of In-house Technical Expertise', 'value': 'lack_expertise'}</t>
+          <t>Lack of In-house Technical Expertise</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'concerns_about_data_privacy_&amp;_security',_'value':_'privacy'}</t>
+          <t>concerns_about_data_privacy_&amp;_security</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Concerns about Data Privacy &amp; Security', 'value': 'privacy'}</t>
+          <t>Concerns about Data Privacy &amp; Security</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'ethical_concerns_/_potential_bias',_'value':_'ethics'}</t>
+          <t>ethical_concerns_/_potential_bias</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Ethical Concerns / Potential Bias', 'value': 'ethics'}</t>
+          <t>Ethical Concerns / Potential Bias</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'difficulty_integrating_with_legacy_systems',_'value':_'integration'}</t>
+          <t>difficulty_integrating_with_legacy_systems</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Difficulty Integrating with Legacy Systems', 'value': 'integration'}</t>
+          <t>Difficulty Integrating with Legacy Systems</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'uncertainty_about_roi',_'value':_'roi_uncertainty'}</t>
+          <t>uncertainty_about_roi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Uncertainty about ROI', 'value': 'roi_uncertainty'}</t>
+          <t>Uncertainty about ROI</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'reduced_need_for_staff_(replaced_by_ai)',_'value':_'reduced'}</t>
+          <t>reduced_need_for_staff_(replaced_by_ai)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Reduced need for staff (Replaced by AI)', 'value': 'reduced'}</t>
+          <t>Reduced need for staff (Replaced by AI)</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'increased_need_for_staff_(new_ai-related_roles)',_'value':_'increased'}</t>
+          <t>increased_need_for_staff_(new_ai-related_roles)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Increased need for staff (New AI-related roles)', 'value': 'increased'}</t>
+          <t>Increased need for staff (New AI-related roles)</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'no_change_in_staffing_levels',_'value':_'no_change'}</t>
+          <t>no_change_in_staffing_levels</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'No change in staffing levels', 'value': 'no_change'}</t>
+          <t>No change in staffing levels</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'shifted_existing_staff_to_higher-value_tasks',_'value':_'shifted'}</t>
+          <t>shifted_existing_staff_to_higher-value_tasks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Shifted existing staff to higher-value tasks', 'value': 'shifted'}</t>
+          <t>Shifted existing staff to higher-value tasks</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'significantly_increase',_'value':_'increase_high'}</t>
+          <t>significantly_increase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Significantly Increase', 'value': 'increase_high'}</t>
+          <t>Significantly Increase</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'slightly_increase',_'value':_'increase_low'}</t>
+          <t>slightly_increase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Slightly Increase', 'value': 'increase_low'}</t>
+          <t>Slightly Increase</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'maintain_current_levels',_'value':_'maintain'}</t>
+          <t>maintain_current_levels</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Maintain Current Levels', 'value': 'maintain'}</t>
+          <t>Maintain Current Levels</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'decrease_investment',_'value':_'decrease'}</t>
+          <t>decrease_investment</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Decrease Investment', 'value': 'decrease'}</t>
+          <t>Decrease Investment</t>
         </is>
       </c>
     </row>
